--- a/config/signal_map.xlsx
+++ b/config/signal_map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangjianhai/02_ADAS/01_repo/01_Tools/01_kpi_extractor/python/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26F7940-EF16-3443-8E4A-E9ACD37E1201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3813F1-2E9E-1E42-A15C-8FBB6DD8542F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="34200" windowHeight="20360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="57">
   <si>
     <t>payload/long_ctrl_accel_request</t>
   </si>
@@ -199,6 +199,12 @@
   </si>
   <si>
     <t>fcw_state_info/time_to_collision</t>
+  </si>
+  <si>
+    <t>active_safety_status/notices/CPM/braking_event_status</t>
+  </si>
+  <si>
+    <t>cpmEventType</t>
   </si>
 </sst>
 </file>
@@ -905,9 +911,18 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="5"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="5"/>
+      <c r="A23" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="5"/>

--- a/config/signal_map.xlsx
+++ b/config/signal_map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangjianhai/02_ADAS/01_repo/01_Tools/01_kpi_extractor/python/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3813F1-2E9E-1E42-A15C-8FBB6DD8542F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F2C201-2319-C948-A2BF-85FCE7869C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="34200" windowHeight="20360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/config/signal_map.xlsx
+++ b/config/signal_map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangjianhai/02_ADAS/01_repo/01_Tools/01_kpi_extractor/python/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F2C201-2319-C948-A2BF-85FCE7869C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BB2A46-3CD9-3B4F-9FD9-C07B6A6C4F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="34200" windowHeight="20360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="62">
   <si>
     <t>payload/long_ctrl_accel_request</t>
   </si>
@@ -205,6 +205,21 @@
   </si>
   <si>
     <t>cpmEventType</t>
+  </si>
+  <si>
+    <t>NearFieldAssistStateInfo</t>
+  </si>
+  <si>
+    <t>daa_state_info/obstruction_position/x</t>
+  </si>
+  <si>
+    <t>daa_state_info/obstruction_position/y</t>
+  </si>
+  <si>
+    <t>cpmLongDist</t>
+  </si>
+  <si>
+    <t>cpmLatDist</t>
   </si>
 </sst>
 </file>
@@ -925,14 +940,32 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="5"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="5"/>
+      <c r="A24" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="5"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="5"/>
+      <c r="A25" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="5"/>

--- a/config/signal_map.xlsx
+++ b/config/signal_map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangjianhai/02_ADAS/01_repo/01_Tools/01_kpi_extractor/python/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BB2A46-3CD9-3B4F-9FD9-C07B6A6C4F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C0F448-4C35-FF4F-9114-C4FF63DA49E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="34200" windowHeight="20360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="71">
   <si>
     <t>payload/long_ctrl_accel_request</t>
   </si>
@@ -220,6 +220,33 @@
   </si>
   <si>
     <t>cpmLatDist</t>
+  </si>
+  <si>
+    <t>active_safety_status/notices/LKA/intervention_status</t>
+  </si>
+  <si>
+    <t>lkaInterventionStatus</t>
+  </si>
+  <si>
+    <t>LaneSupportSystemDebug</t>
+  </si>
+  <si>
+    <t>dtle_actuation_threshold</t>
+  </si>
+  <si>
+    <t>dtleTarget</t>
+  </si>
+  <si>
+    <t>current_DTLE</t>
+  </si>
+  <si>
+    <t>dtle</t>
+  </si>
+  <si>
+    <t>steering_wheel_torque</t>
+  </si>
+  <si>
+    <t>steerWheelTorque</t>
   </si>
 </sst>
 </file>
@@ -968,24 +995,60 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="5"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="5"/>
+      <c r="A26" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="5"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="5"/>
+      <c r="A27" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="5"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="5"/>
+      <c r="A28" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="5"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="5"/>
+      <c r="A29" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="5"/>

--- a/config/signal_map.xlsx
+++ b/config/signal_map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangjianhai/02_ADAS/01_repo/01_Tools/01_kpi_extractor/python/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C0F448-4C35-FF4F-9114-C4FF63DA49E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB1956E-4624-C547-9BB9-5D4640F0C099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="34200" windowHeight="20360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -207,9 +207,6 @@
     <t>cpmEventType</t>
   </si>
   <si>
-    <t>NearFieldAssistStateInfo</t>
-  </si>
-  <si>
     <t>daa_state_info/obstruction_position/x</t>
   </si>
   <si>
@@ -228,9 +225,6 @@
     <t>lkaInterventionStatus</t>
   </si>
   <si>
-    <t>LaneSupportSystemDebug</t>
-  </si>
-  <si>
     <t>dtle_actuation_threshold</t>
   </si>
   <si>
@@ -247,6 +241,12 @@
   </si>
   <si>
     <t>steerWheelTorque</t>
+  </si>
+  <si>
+    <t>lane_support_system_debug</t>
+  </si>
+  <si>
+    <t>nearFieldAssistStateInfo</t>
   </si>
 </sst>
 </file>
@@ -968,13 +968,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>58</v>
-      </c>
       <c r="C24" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D24" t="s">
         <v>41</v>
@@ -982,13 +982,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
         <v>41</v>
@@ -999,10 +999,10 @@
         <v>49</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="D26" t="s">
         <v>48</v>
@@ -1010,13 +1010,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>66</v>
       </c>
       <c r="D27" t="s">
         <v>41</v>
@@ -1024,13 +1024,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D28" t="s">
         <v>41</v>
@@ -1041,10 +1041,10 @@
         <v>36</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D29" t="s">
         <v>41</v>

--- a/config/signal_map.xlsx
+++ b/config/signal_map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangjianhai/02_ADAS/01_repo/01_Tools/01_kpi_extractor/python/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB1956E-4624-C547-9BB9-5D4640F0C099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8BE73E-E2FF-2C4F-A8F2-F309D7643BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="34200" windowHeight="20360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/config/signal_map.xlsx
+++ b/config/signal_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangjianhai/02_ADAS/01_repo/01_Tools/01_kpi_extractor/python/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8BE73E-E2FF-2C4F-A8F2-F309D7643BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{459F6701-3570-0C49-A5D2-05ECDF860AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="700" windowWidth="34200" windowHeight="20360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="45120" yWindow="5480" windowWidth="34200" windowHeight="13760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vbRcSignals" sheetId="1" r:id="rId1"/>

--- a/config/signal_map.xlsx
+++ b/config/signal_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangjianhai/02_ADAS/01_repo/01_Tools/01_kpi_extractor/python/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{459F6701-3570-0C49-A5D2-05ECDF860AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4158EC39-A33B-4D4C-B439-8EA2726FA2D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45120" yWindow="5480" windowWidth="34200" windowHeight="13760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38400" yWindow="5480" windowWidth="34200" windowHeight="13760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vbRcSignals" sheetId="1" r:id="rId1"/>

--- a/config/signal_map.xlsx
+++ b/config/signal_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangjianhai/02_ADAS/01_repo/01_Tools/01_kpi_extractor/python/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C737EAEA-4D66-5140-9FBD-BB87C4CB847A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52749676-A04C-294B-A91A-D8E20A3A0998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17040" yWindow="2660" windowWidth="17380" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15720" yWindow="1900" windowWidth="17380" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vbRcSignals" sheetId="1" r:id="rId1"/>

--- a/config/signal_map.xlsx
+++ b/config/signal_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangjianhai/02_ADAS/01_repo/01_Tools/01_kpi_extractor/python/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52749676-A04C-294B-A91A-D8E20A3A0998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CCC05F9-BC41-4146-859B-2F39EC91E0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15720" yWindow="1900" windowWidth="17380" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="700" windowWidth="34200" windowHeight="20460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vbRcSignals" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="108">
   <si>
     <t>raster</t>
   </si>
@@ -290,6 +290,60 @@
   </si>
   <si>
     <t>lkaPrecondBlk</t>
+  </si>
+  <si>
+    <t>active_safety_status/settings/AEB/actuation_precondition_blocked</t>
+  </si>
+  <si>
+    <t>active_safety_status/settings/AEB/abort_any_active_events</t>
+  </si>
+  <si>
+    <t>aebPrecondBlk</t>
+  </si>
+  <si>
+    <t>aebAbort</t>
+  </si>
+  <si>
+    <t>active_safety_status/settings/FCW/warning_precondition_blocked</t>
+  </si>
+  <si>
+    <t>active_safety_status/settings/FCW/abort_any_active_events</t>
+  </si>
+  <si>
+    <t>fcwPrecondBlk</t>
+  </si>
+  <si>
+    <t>fcwAbort</t>
+  </si>
+  <si>
+    <t>ebaPrecondBlk</t>
+  </si>
+  <si>
+    <t>ebaAbort</t>
+  </si>
+  <si>
+    <t>active_safety_status/settings/DBS/actuation_precondition_blocked</t>
+  </si>
+  <si>
+    <t>active_safety_status/settings/DBS/abort_any_active_events</t>
+  </si>
+  <si>
+    <t>active_safety_status/settings/CPM/actuation_precondition_blocked</t>
+  </si>
+  <si>
+    <t>cpmAbort</t>
+  </si>
+  <si>
+    <t>active_safety_status/settings/CPM/abort_any_active_events</t>
+  </si>
+  <si>
+    <t>active_safety_status/settings/CPM/warning_precondition_blocked</t>
+  </si>
+  <si>
+    <t>cpmWrnPrecondBlk</t>
+  </si>
+  <si>
+    <t>cpmActPrecondBlk</t>
   </si>
 </sst>
 </file>
@@ -674,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.1640625" bestFit="1" customWidth="1"/>
@@ -1201,6 +1255,132 @@
         <v>88</v>
       </c>
     </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38" t="s">
+        <v>90</v>
+      </c>
+      <c r="C38" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" t="s">
+        <v>93</v>
+      </c>
+      <c r="D39" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" t="s">
+        <v>100</v>
+      </c>
+      <c r="C42" t="s">
+        <v>98</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" t="s">
+        <v>99</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" t="s">
+        <v>102</v>
+      </c>
+      <c r="C44" t="s">
+        <v>107</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" t="s">
+        <v>104</v>
+      </c>
+      <c r="C46" t="s">
+        <v>103</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
